--- a/raw_data/实测数据/数据记录_单位换算后.xlsx
+++ b/raw_data/实测数据/数据记录_单位换算后.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\raw_data\实测数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB4524D-02B1-4AC8-9337-508C53804420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C260B4E7-4BDB-46A8-B8D1-2E08D3F9A54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3B48B130-AF04-4D73-8C0F-E5A0AD9E9E6F}"/>
   </bookViews>
@@ -1064,7 +1064,7 @@
   <dimension ref="A1:R49"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="20" max="20" width="17.875" customWidth="1"/>
+    <col min="20" max="20" width="22.875" customWidth="1"/>
     <col min="21" max="21" width="18" customWidth="1"/>
     <col min="23" max="23" width="10.625" customWidth="1"/>
   </cols>
